--- a/packages/calculators/src/modules/test/16-lulucf/16.6-lulucf.xlsx
+++ b/packages/calculators/src/modules/test/16-lulucf/16.6-lulucf.xlsx
@@ -1,20 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/16-lulucf/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B7CF81-13F2-F94E-90C8-DA248FD3DFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7666A530-DCE6-A14A-A9DF-7F632E58B074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="11100" windowWidth="28800" windowHeight="26440" xr2:uid="{A7819E6E-1EF8-024D-B571-91DD1BC0E0B7}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{A7819E6E-1EF8-024D-B571-91DD1BC0E0B7}"/>
   </bookViews>
   <sheets>
     <sheet name="16.6.1.1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -234,6 +232,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cco2" refersTo="='common'!$B$2"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="B2">
+            <v>3.67</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -592,8 +615,8 @@
         <v>17</v>
       </c>
       <c r="T5">
-        <f>44/12</f>
-        <v>3.6666666666666665</v>
+        <f>[1]!common_cco2</f>
+        <v>3.67</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
@@ -723,15 +746,15 @@
       </c>
       <c r="O11">
         <f>$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P11">
         <f>O11*G11*E11</f>
-        <v>11</v>
+        <v>11.01</v>
       </c>
       <c r="Q11">
         <f>O11*M11*F11</f>
-        <v>18.333333333333332</v>
+        <v>18.350000000000001</v>
       </c>
       <c r="T11" t="s">
         <v>33</v>
@@ -883,11 +906,11 @@
       </c>
       <c r="O16">
         <f t="shared" ref="O16" si="3">$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P16">
         <f>O16*G16*E16</f>
-        <v>18.04</v>
+        <v>18.0564</v>
       </c>
       <c r="Q16">
         <f>O16*M16*F16</f>
@@ -1046,15 +1069,15 @@
       </c>
       <c r="O21">
         <f t="shared" ref="O21" si="6">$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P21">
         <f>O21*G21*E21</f>
-        <v>65.999999999999986</v>
+        <v>66.06</v>
       </c>
       <c r="Q21">
         <f>O21*M21*F21</f>
-        <v>87.999999999999986</v>
+        <v>88.08</v>
       </c>
       <c r="S21" t="s">
         <v>30</v>
@@ -1145,7 +1168,7 @@
       </c>
       <c r="O26">
         <f t="shared" ref="O26" si="9">$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P26">
         <f>O26*G26*E26</f>
@@ -1153,7 +1176,7 @@
       </c>
       <c r="Q26">
         <f>O26*M26*F26</f>
-        <v>89.833333333333343</v>
+        <v>89.915000000000006</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.2">
@@ -1229,15 +1252,15 @@
       </c>
       <c r="O31">
         <f t="shared" ref="O31" si="12">$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P31">
         <f>O31*G31*E31</f>
-        <v>100.1</v>
+        <v>100.191</v>
       </c>
       <c r="Q31">
         <f>O31*M31*F31</f>
-        <v>381.33333333333331</v>
+        <v>381.68</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.2">
@@ -1313,15 +1336,15 @@
       </c>
       <c r="O36">
         <f t="shared" ref="O36" si="15">$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P36">
         <f>O36*G36*E36</f>
-        <v>46.199999999999996</v>
+        <v>46.241999999999997</v>
       </c>
       <c r="Q36">
         <f>O36*M36*F36</f>
-        <v>1.3199999999999998</v>
+        <v>1.3211999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.2">
@@ -1397,15 +1420,15 @@
       </c>
       <c r="O41">
         <f t="shared" ref="O41" si="18">$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P41">
         <f>O41*G41*E41</f>
-        <v>56.099999999999994</v>
+        <v>56.150999999999996</v>
       </c>
       <c r="Q41">
         <f>O41*M41*F41</f>
-        <v>5.5</v>
+        <v>5.5049999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.2">
@@ -1481,15 +1504,15 @@
       </c>
       <c r="O46">
         <f t="shared" ref="O46" si="21">$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P46">
         <f>O46*G46*E46</f>
-        <v>2.4566666666666666</v>
+        <v>2.4589000000000003</v>
       </c>
       <c r="Q46">
         <f>O46*M46*F46</f>
-        <v>98.266666666666666</v>
+        <v>98.355999999999995</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
@@ -1565,15 +1588,15 @@
       </c>
       <c r="O51">
         <f t="shared" ref="O51" si="24">$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P51">
         <f>O51*G51*E51</f>
-        <v>15.839999999999996</v>
+        <v>15.854399999999998</v>
       </c>
       <c r="Q51">
         <f>O51*M51*F51</f>
-        <v>44</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
@@ -1649,15 +1672,15 @@
       </c>
       <c r="O56">
         <f t="shared" ref="O56" si="27">$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P56">
         <f>O56*G56*E56</f>
-        <v>66.733333333333334</v>
+        <v>66.793999999999997</v>
       </c>
       <c r="Q56">
         <f>O56*M56*F56</f>
-        <v>286</v>
+        <v>286.26</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
@@ -1709,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="D61">
-        <f t="shared" ref="D61:D65" si="28">IF(C61&lt;=K61, B61,0)</f>
+        <f t="shared" ref="D61:D63" si="28">IF(C61&lt;=K61, B61,0)</f>
         <v>1</v>
       </c>
       <c r="E61">
@@ -1733,15 +1756,15 @@
       </c>
       <c r="O61">
         <f t="shared" ref="O61" si="30">$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P61">
         <f>O61*G61*E61</f>
-        <v>18.04</v>
+        <v>18.0564</v>
       </c>
       <c r="Q61">
         <f>O61*M61*F61</f>
-        <v>22.55</v>
+        <v>22.570499999999999</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
@@ -1879,15 +1902,15 @@
       </c>
       <c r="O71">
         <f>$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P71">
         <f>O71*J71*E71</f>
-        <v>11.131894484412468</v>
+        <v>11.142014388489208</v>
       </c>
       <c r="Q71">
         <f>O71*N71*F71</f>
-        <v>1.8553157474020781</v>
+        <v>1.8570023980815347</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
@@ -1974,15 +1997,15 @@
       </c>
       <c r="O76">
         <f>$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P76">
         <f>O76*G76*E76</f>
-        <v>12.1</v>
+        <v>12.111000000000001</v>
       </c>
       <c r="Q76">
         <f>O76*N76*F76</f>
-        <v>20.166666666666664</v>
+        <v>20.184999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
@@ -2073,15 +2096,15 @@
       </c>
       <c r="O81">
         <f>$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P81">
         <f>O81*J81*E81</f>
-        <v>63.383783783783784</v>
+        <v>63.441405405405412</v>
       </c>
       <c r="Q81">
         <f>O81*N81*F81</f>
-        <v>10.563963963963964</v>
+        <v>10.573567567567569</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
@@ -2168,15 +2191,15 @@
       </c>
       <c r="O86">
         <f>$T$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P86">
         <f>O86*G86*E86</f>
-        <v>7.0714285714285712</v>
+        <v>7.0778571428571428</v>
       </c>
       <c r="Q86">
         <f>O86*N86*F86</f>
-        <v>16.5</v>
+        <v>16.515000000000001</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.2">
